--- a/www/download/IND.surplus_value.empe_ms.r.pc.rpA2.xlsx
+++ b/www/download/IND.surplus_value.empe_ms.r.pc.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>108.1</t>
+          <t>1.08100361645679</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>100.22</t>
+          <t>1.00219306334412</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>109.28</t>
+          <t>1.09278671053769</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>109.22</t>
+          <t>1.09222363889797</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>97.14</t>
+          <t>0.971357223977261</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>103.02</t>
+          <t>1.03020115248255</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>106.01</t>
+          <t>1.060106136729</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>0.958390322413649</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>85.16</t>
+          <t>0.851584376724074</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>63.34</t>
+          <t>0.633370268657737</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>0.56007179635116</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>58.37</t>
+          <t>0.583729427594377</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>54.21</t>
+          <t>0.542067643408209</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>66.36</t>
+          <t>0.663598313756031</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>0.714130990751212</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>0.293874445567698</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>0.32469147071465</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.528016032262806</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>0.496644562540063</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>48.73</t>
+          <t>0.487265322457256</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>0.539019452437066</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>0.508514232941086</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>48.09</t>
+          <t>0.480930674334281</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>0.420827370125362</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>0.332398174511967</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>0.31792227734452</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>0.302798788552646</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>0.295897443975228</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>34.58</t>
+          <t>0.345824388552365</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>0.422346449864975</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0952267442101364</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>0.0607780857800362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>0.118537474609437</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>0.112008040067751</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.0219055947317714</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-0.021075346392544</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-0.0845673186741445</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-0.165091315469403</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-29.43</t>
+          <t>-0.294332009023739</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-35.01</t>
+          <t>-0.350122712285771</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-33.77</t>
+          <t>-0.337652069380704</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-32.52</t>
+          <t>-0.325169545895535</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-30.4</t>
+          <t>-0.304038790005865</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-23.5</t>
+          <t>-0.235023522922756</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-28.34</t>
+          <t>-0.283415213555036</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>489.76</t>
+          <t>4.89755895547756</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>553.79</t>
+          <t>5.53791741330328</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>669.77</t>
+          <t>6.69767107687065</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>472.11</t>
+          <t>4.7210504415112</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>489.95</t>
+          <t>4.89952681747087</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>536.53</t>
+          <t>5.36527534501051</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>514.85</t>
+          <t>5.14849311736373</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>524.5</t>
+          <t>5.24496010748623</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>732.34</t>
+          <t>7.32340292589956</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>505.57</t>
+          <t>5.05565816354821</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>532.21</t>
+          <t>5.32210648871806</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>532.08</t>
+          <t>5.32078096713119</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>492.6</t>
+          <t>4.92600293706383</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>423.86</t>
+          <t>4.2386174140012</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>362.29</t>
+          <t>3.62289665427979</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>251.8</t>
+          <t>2.51798939547118</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>260.19</t>
+          <t>2.60190433498542</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>288.99</t>
+          <t>2.88993931534211</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>294.31</t>
+          <t>2.94307483847319</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>340.7</t>
+          <t>3.40700908417507</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>359.96</t>
+          <t>3.59958853474558</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>382.6</t>
+          <t>3.82596372482122</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>412.74</t>
+          <t>4.12736971767109</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>427.61</t>
+          <t>4.27610153016007</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>420.64</t>
+          <t>4.20640368557213</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>408.8</t>
+          <t>4.08795786292191</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>404.64</t>
+          <t>4.04642946221457</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>402.24</t>
+          <t>4.02241329292071</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>384.8</t>
+          <t>3.84796722481591</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>396.28</t>
+          <t>3.96279691151319</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>133.39</t>
+          <t>1.3339010931221</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>141.84</t>
+          <t>1.41843148716089</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>157.13</t>
+          <t>1.57129325279384</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>143.79</t>
+          <t>1.43792335825647</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>134.54</t>
+          <t>1.34538438922849</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>115.4</t>
+          <t>1.15403735581899</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>103.78</t>
+          <t>1.03782446626119</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>104.78</t>
+          <t>1.04779997326747</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>92.23</t>
+          <t>0.922291490934717</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>84.79</t>
+          <t>0.847857280559042</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>0.726169892756439</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>0.677045964087077</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>0.729986146785261</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>72.04</t>
+          <t>0.720377552719349</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>82.64</t>
+          <t>0.826405195997246</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>0.244595619576496</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>0.312235642258767</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>0.299178492514061</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>0.303258150557191</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>0.310241298571968</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>0.363221324953156</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>0.492903733393644</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>57.42</t>
+          <t>0.574243647886488</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>0.685836021444397</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>83.77</t>
+          <t>0.837657543752851</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>91.09</t>
+          <t>0.910876049205495</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>0.922965493506385</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>118.98</t>
+          <t>1.18975536127272</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>120.75</t>
+          <t>1.20747449622237</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>126.46</t>
+          <t>1.26463566774542</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>143.89</t>
+          <t>1.43893213836482</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>142.58</t>
+          <t>1.42579105080653</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>175.09</t>
+          <t>1.75092739385853</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>163.46</t>
+          <t>1.634577321502</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>147.17</t>
+          <t>1.47167106612215</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>151.05</t>
+          <t>1.51052914551473</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>129.15</t>
+          <t>1.29146142287211</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>120.63</t>
+          <t>1.20632633248937</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>102.77</t>
+          <t>1.02770179067265</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>103.63</t>
+          <t>1.03629957018814</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>107.37</t>
+          <t>1.07365034608386</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>117.59</t>
+          <t>1.1759237357883</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>1.37200044885508</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>110.91</t>
+          <t>1.10907752771166</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>149.62</t>
+          <t>1.49622922054921</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>444.15</t>
+          <t>4.4414655302351</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>284.34</t>
+          <t>2.84342173061373</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>310.83</t>
+          <t>3.1082828691711</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>302.65</t>
+          <t>3.02645563289801</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>306.61</t>
+          <t>3.06609522014533</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>318.98</t>
+          <t>3.18981271927849</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>288.77</t>
+          <t>2.88773101544176</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>2.72796185194315</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>242.17</t>
+          <t>2.4217135803709</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>224.88</t>
+          <t>2.24880734263791</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>214.11</t>
+          <t>2.1410518935122</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>224.73</t>
+          <t>2.24726543309723</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>221.98</t>
+          <t>2.21976041582443</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>225.39</t>
+          <t>2.25393449499672</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>267.52</t>
+          <t>2.67520846143841</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.201987770343302</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>0.30102911125288</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>0.465417669824157</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>0.418684605422473</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>0.358394387987123</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>0.301439073555613</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>0.319407450659395</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>0.311715124701403</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>0.16198053776098</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>0.127160582684103</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>0.178221691857977</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>0.188572669397674</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>0.181217762761364</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>0.234673904893349</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>0.263944090174338</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>0.0993646294947053</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>0.110372604566193</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>0.370250706400908</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>0.291598665269709</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>0.28349864977321</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>0.339672297633988</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>0.280560530770132</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>0.215525895273565</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>0.0493185405962546</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>0.035661294569614</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.034863375141583</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.0239106421602557</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.0263555074933579</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>0.078649178182846</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>0.178603095320906</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>1.02752920658641</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>110.28</t>
+          <t>1.10275770481481</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>146.75</t>
+          <t>1.46749360704004</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>1.25737925745578</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>113.67</t>
+          <t>1.13671700736096</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>114.46</t>
+          <t>1.14460501218717</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>104.37</t>
+          <t>1.04370643786818</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>94.24</t>
+          <t>0.942358709423741</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>0.909666033260323</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>68.43</t>
+          <t>0.684302340279535</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>66.35</t>
+          <t>0.663521066637239</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>62.11</t>
+          <t>0.621140336900642</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>0.641954299177885</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>64.75</t>
+          <t>0.647478658839022</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>0.80770018265356</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>354.55</t>
+          <t>3.54545334419024</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>335.1</t>
+          <t>3.35102820617744</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>327.38</t>
+          <t>3.27380002029605</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>311.71</t>
+          <t>3.11714870840385</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>320.15</t>
+          <t>3.20151418116409</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>272.41</t>
+          <t>2.7241226118703</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>267.36</t>
+          <t>2.67363708936169</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>197.03</t>
+          <t>1.97031851896595</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>156.49</t>
+          <t>1.56489773957989</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>144.26</t>
+          <t>1.44259484931642</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>167.19</t>
+          <t>1.67193822958301</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>173.51</t>
+          <t>1.73513034780913</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>154.56</t>
+          <t>1.54564930754338</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>131.79</t>
+          <t>1.31794246864906</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>130.35</t>
+          <t>1.30354657694133</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>66.99</t>
+          <t>0.669938836517986</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>0.640720172636576</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>0.923834652052299</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>0.802012715865545</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>78.56</t>
+          <t>0.785627554935189</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>93.87</t>
+          <t>0.93873020992833</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>0.861345069493512</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>84.01</t>
+          <t>0.840076124512491</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>65.44</t>
+          <t>0.654385562941185</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>0.608475099048507</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>0.587806314677317</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>0.563393025360042</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>0.60475473698617</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>63.92</t>
+          <t>0.639206887658833</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>70.75</t>
+          <t>0.707544639357358</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>0.747346034204016</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>0.697906410919354</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>91.62</t>
+          <t>0.916189786945521</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>0.753768344759163</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>62.67</t>
+          <t>0.626710516347025</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>0.62262459332116</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>0.538599924121556</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>0.440385183506886</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>0.358524254504515</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>0.263725630781259</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>0.255062739789611</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>0.266767844860027</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>0.28492902881738</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>0.323200368250785</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>0.418078236250613</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>110.91</t>
+          <t>1.10908910125164</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>1.1050398778544</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>122.91</t>
+          <t>1.22914716160524</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>105.23</t>
+          <t>1.05234079513068</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>93.25</t>
+          <t>0.932450690087375</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>0.862217883751697</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>76.91</t>
+          <t>0.769104700842656</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>70.04</t>
+          <t>0.700429055615399</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>0.589673521175199</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>0.503622472258032</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>0.514647286932304</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>0.499554640006631</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>0.524743994256853</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>0.717952953501012</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>80.52</t>
+          <t>0.805219316342827</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>285.05</t>
+          <t>2.8505088138183</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>257.01</t>
+          <t>2.57005206766109</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>258.84</t>
+          <t>2.58835261781403</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>252.13</t>
+          <t>2.52133869764637</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>225.21</t>
+          <t>2.25212428826321</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>202.59</t>
+          <t>2.02590426383754</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>221.97</t>
+          <t>2.21965535406599</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>184.13</t>
+          <t>1.84131706410117</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>187.73</t>
+          <t>1.8773205959778</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>167.75</t>
+          <t>1.67746106325743</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>173.01</t>
+          <t>1.73012381873632</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>165.83</t>
+          <t>1.65825583628811</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>148.53</t>
+          <t>1.48532406535179</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>148.45</t>
+          <t>1.48448252829265</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>142.42</t>
+          <t>1.42415023277383</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>211.52</t>
+          <t>2.11519791956236</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>227.87</t>
+          <t>2.27869373192011</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>252.08</t>
+          <t>2.52082402660679</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>263.22</t>
+          <t>2.63215028568579</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>261.63</t>
+          <t>2.61631848614789</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>260.69</t>
+          <t>2.60688697190619</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>278.42</t>
+          <t>2.78422897795042</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>254.42</t>
+          <t>2.54422105943776</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>242.45</t>
+          <t>2.42447406228631</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>277.61</t>
+          <t>2.77614444937047</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>285.22</t>
+          <t>2.85217687677015</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>304.25</t>
+          <t>3.04254742640407</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>293.36</t>
+          <t>2.93360736122264</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>323.58</t>
+          <t>3.23576077334226</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>343.72</t>
+          <t>3.43719952715307</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>207.86</t>
+          <t>2.07859867026162</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>234.71</t>
+          <t>2.34710791776997</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>252.23</t>
+          <t>2.52234687888774</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>307.97</t>
+          <t>3.07974380989359</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>332.47</t>
+          <t>3.32470467859632</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>304.42</t>
+          <t>3.04422383695269</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>271.35</t>
+          <t>2.71347645776001</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>244.97</t>
+          <t>2.44970406808779</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>228.14</t>
+          <t>2.2813634810201</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>199.68</t>
+          <t>1.99675171867071</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>208.56</t>
+          <t>2.08561992687412</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>217.97</t>
+          <t>2.17965830051752</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>200.27</t>
+          <t>2.00268502072703</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>208.29</t>
+          <t>2.08289747731468</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>213.1</t>
+          <t>2.13100191915199</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>0.69487522811677</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>86.12</t>
+          <t>0.861233695727672</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>0.765019673013676</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>0.77802008528808</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>81.09</t>
+          <t>0.810941874852625</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>0.873850407592165</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>0.893746495082068</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>97.88</t>
+          <t>0.978798247125535</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>0.937342165821188</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>0.900419522208185</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>85.31</t>
+          <t>0.853074660872268</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>80.89</t>
+          <t>0.808883751612667</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>0.852398295561916</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>0.911981832136713</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>83.77</t>
+          <t>0.83768006963192</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>0.953016376241808</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>0.898999155286363</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>114.39</t>
+          <t>1.14385968936815</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>123.75</t>
+          <t>1.23749760623584</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>122.87</t>
+          <t>1.22873229985951</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>119.87</t>
+          <t>1.1987328317418</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>1.00424884895346</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>0.889214476672416</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>105.85</t>
+          <t>1.05846277061869</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>114.35</t>
+          <t>1.1434897464261</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>110.58</t>
+          <t>1.10581107899543</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>119.44</t>
+          <t>1.19439807447079</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>101.45</t>
+          <t>1.01448377938534</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>84.57</t>
+          <t>0.845748211897202</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>0.632480043326047</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>108.61</t>
+          <t>1.08610973969103</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>106.43</t>
+          <t>1.06427119856242</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>122.86</t>
+          <t>1.228578310817</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>118.81</t>
+          <t>1.18814262483581</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>113.75</t>
+          <t>1.13752638307827</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>115.93</t>
+          <t>1.15930153122636</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>98.95</t>
+          <t>0.989495267857273</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>87.76</t>
+          <t>0.877607195478178</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>83.12</t>
+          <t>0.831203997618111</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>0.570217425752171</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>54.25</t>
+          <t>0.542507934610207</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>0.49895344457737</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>55.44</t>
+          <t>0.554434054844215</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>67.19</t>
+          <t>0.671856563455826</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>80.97</t>
+          <t>0.80966804724733</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>0.836332461418831</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>103.46</t>
+          <t>1.03457087898697</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>122.08</t>
+          <t>1.22080379682726</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>125.45</t>
+          <t>1.25449883004651</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>108.58</t>
+          <t>1.0858216552075</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>0.981987206069746</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>0.995972005358446</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>107.16</t>
+          <t>1.07163584787874</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>101.69</t>
+          <t>1.01688072447606</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>93.05</t>
+          <t>0.930485524012193</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>0.913984309489264</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>98.91</t>
+          <t>0.989142717340987</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>114.38</t>
+          <t>1.1437806422936</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>113.32</t>
+          <t>1.13324575885986</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>101.57</t>
+          <t>1.01573830833141</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>101.15</t>
+          <t>1.01145790629327</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>104.27</t>
+          <t>1.04274553674349</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>1.20503040896531</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>124.26</t>
+          <t>1.24262114070666</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>137.09</t>
+          <t>1.37088950212766</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>125.16</t>
+          <t>1.25164729039918</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>131.32</t>
+          <t>1.31319825891324</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>127.95</t>
+          <t>1.27953704799</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>114.65</t>
+          <t>1.14648612299703</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>112.87</t>
+          <t>1.1287459300215</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>116.86</t>
+          <t>1.16862519320123</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>110.88</t>
+          <t>1.10875768351422</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>114.62</t>
+          <t>1.14616738871975</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>127.16</t>
+          <t>1.27159970625327</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>129.53</t>
+          <t>1.295250665708</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>304.94</t>
+          <t>3.04943422863649</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>285.75</t>
+          <t>2.85749448636563</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>283.16</t>
+          <t>2.83164275709472</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>237.32</t>
+          <t>2.37324093346177</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>220.19</t>
+          <t>2.20192593212041</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>227.48</t>
+          <t>2.27477707313362</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>230.3</t>
+          <t>2.30295901059937</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>218.45</t>
+          <t>2.18448730149816</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>186.47</t>
+          <t>1.86472795000284</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>227.44</t>
+          <t>2.2744371807945</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>219.41</t>
+          <t>2.19412277232584</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>210.31</t>
+          <t>2.10313111621365</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>215.08</t>
+          <t>2.15081884805971</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>202.01</t>
+          <t>2.02009882556189</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>2.09799200491953</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>0.212445009011197</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>0.388789423195916</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>65.31</t>
+          <t>0.653129073506509</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>0.703528084998714</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>66.04</t>
+          <t>0.66040678480842</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>0.653466499615134</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>0.770993264733694</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>64.98</t>
+          <t>0.649775553313577</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>0.66948339804637</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>0.586043722080994</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>55.83</t>
+          <t>0.558347933416593</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>0.573722708030856</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>76.38</t>
+          <t>0.763843669496188</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>0.575473236334025</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>88.85</t>
+          <t>0.888523421244663</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>320.17</t>
+          <t>3.20168476015631</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>291.61</t>
+          <t>2.91609392052946</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>301.1</t>
+          <t>3.01096178470978</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>314.21</t>
+          <t>3.14205424892323</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>311.37</t>
+          <t>3.11372900133093</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>373.58</t>
+          <t>3.73578473769273</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>383.13</t>
+          <t>3.83126750636343</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>402.56</t>
+          <t>4.02555044992054</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>373.09</t>
+          <t>3.73088076154055</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>369.84</t>
+          <t>3.6983735597654</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>341.69</t>
+          <t>3.41686411158875</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>305.83</t>
+          <t>3.05831861965</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>264.61</t>
+          <t>2.64610626610696</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>237.71</t>
+          <t>2.37709161734775</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>282.52</t>
+          <t>2.8252469861343</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>309.14</t>
+          <t>3.09142495557962</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>325.95</t>
+          <t>3.25946427618487</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>348.51</t>
+          <t>3.48509010209012</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>324.19</t>
+          <t>3.24192219549142</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>309.71</t>
+          <t>3.09713478229418</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>300.63</t>
+          <t>3.00633267105245</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>263.53</t>
+          <t>2.63534310389329</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>265.86</t>
+          <t>2.65861170464332</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>275.4</t>
+          <t>2.75401625158</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>291.77</t>
+          <t>2.91767286855795</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>284.35</t>
+          <t>2.84346874059985</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>311.71</t>
+          <t>3.11710988159305</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>323.95</t>
+          <t>3.23952692852552</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>332.1</t>
+          <t>3.32104246638399</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>335.77</t>
+          <t>3.35768961471732</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>205.2</t>
+          <t>2.05200709475523</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>182.11</t>
+          <t>1.82106674962404</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>243.88</t>
+          <t>2.4387554511913</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>215.82</t>
+          <t>2.15815056193225</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>1.72769187525385</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>153.98</t>
+          <t>1.53979866809314</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>89.67</t>
+          <t>0.896699907379644</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>108.95</t>
+          <t>1.08946098857587</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>141.49</t>
+          <t>1.41487585723537</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>133.63</t>
+          <t>1.33626814712358</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>130.56</t>
+          <t>1.30557022241172</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>140.28</t>
+          <t>1.40281934718043</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>128.74</t>
+          <t>1.28743577490761</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>115.06</t>
+          <t>1.15063524042548</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>1.41196129066721</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.0171983664937618</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.0071714899390849</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>0.452330702024385</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>0.20147940970177</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>0.155965042348856</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>18.61</t>
+          <t>0.186056446655063</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>0.0717065694419889</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>-0.0410143757660402</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.00462489582665859</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-0.0299693407041688</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.00489113292051968</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.011730081706669</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.0137435739931819</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-0.0434495614660824</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.0237973670830113</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>133.68</t>
+          <t>1.33679174153848</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>121.16</t>
+          <t>1.21163205994336</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>116.79</t>
+          <t>1.16789682215832</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>112.22</t>
+          <t>1.122165468216</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>131.76</t>
+          <t>1.3176399045609</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>145.86</t>
+          <t>1.45856553666199</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>209.67</t>
+          <t>2.09667724171296</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>218.34</t>
+          <t>2.18342487044159</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>228.37</t>
+          <t>2.2836621244041</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>252.22</t>
+          <t>2.52222505588563</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>239.17</t>
+          <t>2.39172317922458</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>249.96</t>
+          <t>2.49963589399246</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>256.56</t>
+          <t>2.56559593717258</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>233.87</t>
+          <t>2.33867334952557</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>258.94</t>
+          <t>2.58943029978565</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>140.03</t>
+          <t>1.40029322808974</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>133.97</t>
+          <t>1.33966681779241</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>173.86</t>
+          <t>1.73857814081844</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>140.74</t>
+          <t>1.40742219741338</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>145.02</t>
+          <t>1.45018352407529</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>139.04</t>
+          <t>1.39042698174054</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>127.31</t>
+          <t>1.27310365652341</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>131.13</t>
+          <t>1.31125401223252</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>201.39</t>
+          <t>2.01391964832008</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>126.61</t>
+          <t>1.26605685865411</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>129.12</t>
+          <t>1.29122014163166</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>156.2</t>
+          <t>1.56202398143265</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>159.16</t>
+          <t>1.59161970536736</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>148.68</t>
+          <t>1.48677353763931</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>193.46</t>
+          <t>1.93458646729424</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>282.38</t>
+          <t>2.82384456464946</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>301.65</t>
+          <t>3.01649326584128</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>347.21</t>
+          <t>3.47214254093425</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>266.66</t>
+          <t>2.66663600812913</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>271.99</t>
+          <t>2.7198894126121</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>218.36</t>
+          <t>2.18362174769623</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>204.09</t>
+          <t>2.04091886324485</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>287.06</t>
+          <t>2.8705571440834</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>424.59</t>
+          <t>4.24587615675059</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>317.89</t>
+          <t>3.17885877344565</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>270.17</t>
+          <t>2.70165399628295</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>276.21</t>
+          <t>2.7621438280033</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>248.7</t>
+          <t>2.48695952242241</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>227.9</t>
+          <t>2.27901365336955</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>2.69396539321804</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>135.17</t>
+          <t>1.35171244271844</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>121.72</t>
+          <t>1.21721459188775</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>142.92</t>
+          <t>1.42917665093182</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>156.36</t>
+          <t>1.56362040874013</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>170.56</t>
+          <t>1.70558970606752</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>143.01</t>
+          <t>1.43011091322938</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>151.63</t>
+          <t>1.51634518959048</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>147.06</t>
+          <t>1.47057680565492</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>129.49</t>
+          <t>1.29494914428451</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>120.87</t>
+          <t>1.20869737065973</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>117.68</t>
+          <t>1.17681935886196</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>122.63</t>
+          <t>1.22633690706524</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>106.29</t>
+          <t>1.06285110939776</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>0.8130047558744</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>79.54</t>
+          <t>0.79537642237747</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>483.16</t>
+          <t>4.83158770418826</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>453.61</t>
+          <t>4.53610625196598</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>464.63</t>
+          <t>4.64625973085063</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>461.25</t>
+          <t>4.61251011106848</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>495.27</t>
+          <t>4.95273840175338</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>474.56</t>
+          <t>4.74555020537083</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>456.03</t>
+          <t>4.56025038484924</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>451.3</t>
+          <t>4.5129788070739</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>384.19</t>
+          <t>3.84189329914575</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>310.61</t>
+          <t>3.10613698158648</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>317.28</t>
+          <t>3.17275213631016</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>296.06</t>
+          <t>2.96064829648802</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>231.52</t>
+          <t>2.31523902358495</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>242.52</t>
+          <t>2.42520140405947</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>178.08</t>
+          <t>1.78079506246257</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>1.0313778783209</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>108.13</t>
+          <t>1.08130674935741</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>131.95</t>
+          <t>1.31952795164503</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>121.32</t>
+          <t>1.21320112619477</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>118.94</t>
+          <t>1.18941073050894</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>123.99</t>
+          <t>1.239930997898</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>113.46</t>
+          <t>1.13458430830955</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>110.9</t>
+          <t>1.10902390671242</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>0.907046418816926</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>96.58</t>
+          <t>0.965753814824007</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>1.05004509640679</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>103.17</t>
+          <t>1.03174085752571</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>107.39</t>
+          <t>1.07392814852191</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>55.06</t>
+          <t>0.550637475794789</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>56.06</t>
+          <t>0.560571472046865</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>0.710819639399123</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>64.31</t>
+          <t>0.643077130040694</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>0.860486219469035</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>0.720168607225191</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>70.69</t>
+          <t>0.706889644376488</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>54.51</t>
+          <t>0.54510247240292</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>0.522847110367251</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>0.450439460110542</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>0.335592104694987</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>0.287186360142945</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>0.254448310319358</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>0.260213841708357</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>0.223731778186751</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>0.36281734069701</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>0.515170490233493</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>338.87</t>
+          <t>3.38868266841154</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>292.9</t>
+          <t>2.92902020661703</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>279.12</t>
+          <t>2.79117266743105</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>274.2</t>
+          <t>2.74200345603273</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>257.48</t>
+          <t>2.57476675219091</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>314.77</t>
+          <t>3.14767990653802</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>359.21</t>
+          <t>3.59207086135524</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>435.85</t>
+          <t>4.35847533795854</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>401.2</t>
+          <t>4.01199862421258</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>354.26</t>
+          <t>3.54257997801001</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>366.31</t>
+          <t>3.66313545717944</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>376.4</t>
+          <t>3.76397362072495</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>357.79</t>
+          <t>3.57794018759569</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>1.48798782809388</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>182.05</t>
+          <t>1.82052193212652</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>115.52</t>
+          <t>1.15516695898539</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>100.86</t>
+          <t>1.0085847040749</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>122.61</t>
+          <t>1.22612901473846</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>126.68</t>
+          <t>1.26679949939643</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>125.54</t>
+          <t>1.25541751029266</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>113.29</t>
+          <t>1.13293260319054</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>105.16</t>
+          <t>1.0515550901491</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>1.08683329446237</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>108.46</t>
+          <t>1.08464995515362</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>112.32</t>
+          <t>1.12321482285089</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>112.39</t>
+          <t>1.1238747914209</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>118.52</t>
+          <t>1.18517757232822</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>138.88</t>
+          <t>1.38880850779909</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>143.39</t>
+          <t>1.43387637383628</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>160.95</t>
+          <t>1.60945294061464</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>116.81</t>
+          <t>1.16809604824328</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>118.64</t>
+          <t>1.18642926504756</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>122.3</t>
+          <t>1.22304763704094</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>111.28</t>
+          <t>1.11281733038523</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>1.04318943518884</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>0.912662009229841</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>0.822760906090115</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>75.32</t>
+          <t>0.753150347333491</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>70.77</t>
+          <t>0.707686473705158</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>69.76</t>
+          <t>0.697637582179089</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>0.695273326713401</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>74.54</t>
+          <t>0.745424041741351</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>0.811994088093919</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>88.71</t>
+          <t>0.887104280365055</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>0.907384080755075</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>0.0873712495192687</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>0.133122592703104</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>0.107644655760385</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>0.0955403589012565</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>0.0839813117101873</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.054014386351273</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.0557907000693965</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>0.0754881458769412</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>0.150421125590984</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>0.190890376326781</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>0.189503928374582</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>0.199161332794719</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>0.292339976197499</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>0.310169320915963</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>0.33774951563908</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>0.557953052108528</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>60.98</t>
+          <t>0.609837517789126</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>0.623089564219576</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>0.60626869629476</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>59.35</t>
+          <t>0.593514958812601</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>0.560102937486231</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>0.566845337231621</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>0.582042038295091</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>0.607100839765454</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>62.33</t>
+          <t>0.623303979891331</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>62.29</t>
+          <t>0.62287878913123</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>0.633754582559104</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>72.07</t>
+          <t>0.720732596404075</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>0.733990505805978</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>0.757247082047407</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
